--- a/output/2026-09-07_01_Slovenia_Gorenjska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-07_01_Slovenia_Gorenjska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -559,7 +559,6 @@
           <t>TALCOM, podjetje za trgovino, inženiring in svetovanje, Škofja Loka, d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Škofja Loka</t>
@@ -666,7 +665,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rivenditore/rappresentante di utensili da taglio e precisione per orodjarstvo e industria metalmeccanica (marchi Cogo, Nachreiner, Palbit, Enwa, ecc.). Verificata via sito ufficiale e moja-dejavnost.si.</t>
+          <t>Rivenditore/rappresentante di utensili da taglio e precisione per orodjarstvo e industria metalmeccanica (marchi Cogo, Nachreiner, Palbit, Enwa, ecc.). Verificata via sito ufficiale e moja-dejavnost.si. [DUPLICATO — vedi anche: 2026-09-07_00_Slovenia_Gorenjska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">

--- a/output/2026-09-07_01_Slovenia_Gorenjska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-07_01_Slovenia_Gorenjska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
